--- a/validation/tables/supplementary_per_locus.xlsx
+++ b/validation/tables/supplementary_per_locus.xlsx
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.511</v>
+        <v>0.512</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
